--- a/artfynd/A 31735-2025 artfynd.xlsx
+++ b/artfynd/A 31735-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80557215</v>
+        <v>80557095</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586659.9150118099</v>
+        <v>586666</v>
       </c>
       <c r="R2" t="n">
-        <v>7171160.808422083</v>
+        <v>7171145</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80557095</v>
+        <v>80557215</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586665.9451766758</v>
+        <v>586660</v>
       </c>
       <c r="R3" t="n">
-        <v>7171145.116573216</v>
+        <v>7171161</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
